--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-002_出勤打刻_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-002_出勤打刻_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="10363200"/>
+    <ext cx="8572500" cy="10572750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-002 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-002 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>INACTIVE にされたユーザーでも、発行済みトークンの有効期限（8時間）内は打刻できる（トークン失効は未対応。ONL-001 と同じ制約）。updated_at は UPDATE 時に DB トリガ（set_updated_at）が自動更新する（アプリは設定しない）。</t>
+          <t>INACTIVE にされたユーザーでも、発行済みトークンの有効期限（2時間）内は打刻できる（トークン失効は未対応。ONL-001 と同じ制約）。updated_at は UPDATE 時に DB トリガ（set_updated_at）が自動更新する（アプリは設定しない）。</t>
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="49" customHeight="1">
+    <row r="3" ht="79" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -1864,7 +1864,8 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：tables を C/R/U に訂正（既存行への UPDATE があるため）、updated_at をトリガ自動更新に変更、トークン不正を 401 / E-001 の JSON に更新</t>
+          <t>・確定設計変更 D1〜D10 を反映：tables を C/R/U に訂正（既存行への UPDATE があるため）、updated_at をトリガ自動更新に変更、トークン不正を 401 / E-001 の JSON に更新
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、トークン有効期限を2時間に更新（コードを正とする）</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -3109,7 +3110,7 @@
       <c r="E3" s="9" t="n"/>
       <c r="F3" s="10" t="n"/>
     </row>
-    <row r="4" ht="49" customHeight="1">
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>①</t>
@@ -3122,7 +3123,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Controller: Long.valueOf(jwt.getSubject())。リクエストに userId は含めない（なりすまし防止）</t>
+          <t>Controller: Long.valueOf(auth.getName())。リクエストに userId は含めない（なりすまし防止）</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -3386,7 +3387,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>public ClockInResponse clockIn(@AuthenticationPrincipal Jwt jwt)</t>
+          <t>public ClockInResponse clockIn(Authentication auth)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -3450,17 +3451,17 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン（Spring Security が注入）。sub = users.id</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -3507,7 +3508,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>1. Long userId = Long.valueOf(jwt.getSubject());
+          <t>1. Long userId = Long.valueOf(auth.getName());
 2. return attendanceService.clockIn(userId);</t>
         </is>
       </c>

--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-002_出勤打刻_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-002_出勤打刻_オンライン詳細設計書.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-002 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜026)の概要。本書はそのうち ONL-002 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1786,7 +1786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1869,6 +1869,29 @@
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="79" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>他処理（ONL-003/024/025）との整合を確認して更新：Entity は AttendanceRecord(userId, workDate) コンストラクタで生成する実装に合わせて ⑤ の記述を修正、クラス一覧に ONL-024/025 によるメソッド追加を追記、401 のメッセージを実装に合わせて「認証が必要です。再度ログインしてください。」に修正。出勤打刻の処理内容自体に変更はない</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1882,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F37"/>
+  <dimension ref="A2:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2257,138 +2280,126 @@
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="10" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>ONL-024/025</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席開始／終了</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>同じ AttendanceController / AttendanceService / Clock を使う。出勤後に休憩・離席を打刻でき、clock_in が無い日は E-007</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>1.3 対象クラス一覧（パッケージ：com.example.kintaiflow）</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>パッケージ</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>クラス名</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>責務</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>ファイル</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>新規/既存</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="64" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="28" ht="94" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>controller</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>AttendanceController</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Controller</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>打刻・月次勤怠の API 入口（本処理で clockIn を定義。ONL-003 が clockOut、ONL-004 が getMonthly を追加）</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>打刻・月次勤怠の API 入口（本処理で clockIn を定義。ONL-003 が clockOut、ONL-004 が getMonthly、ONL-024/025 が breakStart / breakEnd を追加）</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>controller/AttendanceController.java</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="49" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="29" ht="49" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>AttendanceService</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>出勤打刻の業務ロジック（本処理で clockIn を定義。ONL-003/004 でメソッド追加）</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>出勤打刻の業務ロジック（本処理で clockIn を定義。ONL-003/004/024/025 でメソッド追加）</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>service/AttendanceService.java</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>新規</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>repository</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>AttendanceRecordRepository</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Repository</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>attendance_records の検索（行ロック付き）・保存</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>repository/AttendanceRecordRepository.java</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -2400,27 +2411,27 @@
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>entity</t>
+          <t>repository</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>AttendanceRecord</t>
+          <t>AttendanceRecordRepository</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>attendance_records テーブルのマッピング</t>
+          <t>attendance_records の検索（行ロック付き）・保存</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>entity/AttendanceRecord.java</t>
+          <t>repository/AttendanceRecordRepository.java</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -2432,128 +2443,128 @@
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceRecord</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>attendance_records テーブルのマッピング</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>entity/AttendanceRecord.java</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
           <t>dto</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>ClockInResponse</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>DTO(record)</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>出勤打刻の正常応答（workDate, clockIn）</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>dto/ClockInResponse.java</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="49" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="33" ht="49" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>ClockConfig</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>java.time.Clock Bean（Asia/Tokyo）。時刻取得を差し替え可能にしてテスト容易にする</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>config/ClockConfig.java</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="64" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>AppTime</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Utility</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>JST 定数 ZONE と、LocalDateTime → ISO 8601 文字列(+09:00) 変換 toIso()。全処理で共用</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>config/AppTime.java</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>新規</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>exception</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>BusinessException</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Exception</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>業務エラー（コード・HTTPステータス保持）</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>exception/BusinessException.java</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>既存（ONL-001 で定義）</t>
         </is>
       </c>
     </row>
@@ -2565,101 +2576,134 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
+          <t>BusinessException</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>業務エラー（コード・HTTPステータス保持）</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>exception/BusinessException.java</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-001 で定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
           <t>GlobalExceptionHandler</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>ControllerAdvice</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>例外→共通エラー応答への変換</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>exception/GlobalExceptionHandler.java</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001 で定義）</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>dto</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>ErrorResponse</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>DTO(record)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>共通エラー応答</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>dto/ErrorResponse.java</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001 で定義）</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="49" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="38" ht="49" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>SecurityConfig</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>JWT 認証（ログイン API 以外は authenticated）。本処理での変更なし</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>config/SecurityConfig.java</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001 で定義）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C18:F18"/>
@@ -2668,6 +2712,7 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="C24:F24"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C16:F16"/>
@@ -2676,7 +2721,6 @@
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3017,7 +3061,7 @@
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="10" t="n"/>
     </row>
-    <row r="16" ht="94" customHeight="1">
+    <row r="16" ht="79" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
           <t>エラー例</t>
@@ -3028,7 +3072,7 @@
           <t>HTTP 409
 { "code": "E-006", "message": "本日は既に打刻済みです。", "fieldErrors": [] }
 HTTP 401（トークンなし・期限切れ・不正。AuthenticationEntryPoint が返す JSON。Controller には到達しない）
-{ "code": "E-001", "message": "認証情報が無効、または有効期限が切れています。再度ログインしてください。", "fieldErrors": [] }</t>
+{ "code": "E-001", "message": "認証が必要です。再度ログインしてください。", "fieldErrors": [] }</t>
         </is>
       </c>
       <c r="C16" s="9" t="n"/>
@@ -3701,7 +3745,7 @@
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="10" t="n"/>
     </row>
-    <row r="24" ht="349" customHeight="1">
+    <row r="24" ht="319" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -3719,9 +3763,7 @@
     throw new BusinessException("E-006",
         "本日は既に打刻済みです。", HttpStatus.CONFLICT);
 if (rec == null) {                                           // ⑤ 行なし → 新規
-    rec = new AttendanceRecord();
-    rec.setUserId(userId);
-    rec.setWorkDate(today);
+    rec = new AttendanceRecord(userId, today);   // コンストラクタで userId / workDate を設定
 }                       // 行あり(clock_in が NULL)の場合は既存行を再利用
 rec.setClockIn(now);
 try {
@@ -3765,7 +3807,7 @@
         <is>
           <t>【二重打刻の防止】本日の行が既にある場合は FOR UPDATE で行ロックし、同一ユーザーの並行リクエストを直列化する。行がまだ無い場合は2つのリクエストが同時に INSERT を試みるが、uq_attendance_records_1 により後続は先行のコミットまで待たされた後に一意制約違反となり、⑦で E-006 になる。
 【catch の対象】DataIntegrityViolationException はすべて E-006 に変換してよい（users は物理削除しないため、FK 違反は実運用で発生しない）。catch 後は例外を投げるのでトランザクションはロールバックされる（PostgreSQL ではエラー後に同一トランザクションで SQL を発行しない）。
-【行ありで clock_in が NULL】通常は発生しない（打刻修正承認 ONL-010 は clock_in/clock_out を両方設定する）が、防御的に既存行を再利用して clock_in を設定する。
+【行ありで clock_in が NULL】通常は発生しない（打刻修正承認 ONL-010 は clock_in/clock_out を両方設定する。休憩・離席の打刻 ONL-024 は clock_in が NULL の行には打刻できない）が、防御的に既存行を再利用して clock_in を設定する。
 【日付】work_date は出勤打刻時点の JST の日付。日跨ぎ勤務は考慮しない（深夜0時を過ぎて打刻すると翌日扱い）。祝日・休日でも打刻可（HolidayService は使用しない）。
 【時刻】クライアントから時刻は受け取らない。Instant/ZonedDateTime ではなく LocalDateTime（JST の壁時計時刻）で保存する。</t>
         </is>
@@ -4578,7 +4620,7 @@
       <c r="E80" s="9" t="n"/>
       <c r="F80" s="10" t="n"/>
     </row>
-    <row r="81" ht="199" customHeight="1">
+    <row r="81" ht="244" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -4597,7 +4639,9 @@
     @Column(name = "overtime_minutes")            private Integer overtimeMinutes;
     @Column(name = "created_at", insertable = false, updatable = false) private LocalDateTime createdAt;
     @Column(name = "updated_at", insertable = false, updatable = false) private LocalDateTime updatedAt;
-    // フィールドは private。getter / setter を持つ（ONL-001 の User と同じ流儀）。リレーション(@ManyToOne)は張らない。
+    protected AttendanceRecord() {}                                   // JPA 用
+    public AttendanceRecord(Long userId, LocalDate workDate) { ... }   // 新規行の作成（出勤打刻・打刻修正の承認で使用）
+    // フィールドは private。getter を持ち、setter は clockIn / clockOut / workMinutes / overtimeMinutes のみ。リレーション(@ManyToOne)は張らない。
 }</t>
         </is>
       </c>
